--- a/Assessment Questions/CDA/ADA-134/DATA ANALYTICS FOUNDATION/. Application of Business Analytics/. Application of Business Analytics.xlsx
+++ b/Assessment Questions/CDA/ADA-134/DATA ANALYTICS FOUNDATION/. Application of Business Analytics/. Application of Business Analytics.xlsx
@@ -1,138 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manfo\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C97C4DDC-EBDA-4D18-AD4D-8E640282F44C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A2A51DF0-66A9-4C26-A7A9-E5D30EE9666E}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
-  <si>
-    <t>Section,Type,Q.No,Scenario,Question,Option A,Option B,Option C,Option D,Correct Answer</t>
-  </si>
-  <si>
-    <t>SECTION A: Medium Level MCQs,MCQ,1,,Customer churn analysis is an application of business analytics used to:,Predict which customers are likely to stop doing business,Calculate employee salaries,Design new products,Schedule maintenance,A</t>
-  </si>
-  <si>
-    <t>SECTION A: Medium Level MCQs,MCQ,2,,Price optimization using analytics helps businesses:,Set random prices,Find the optimal price to maximize profit or revenue,Always set the lowest price,Ignore competitor pricing,B</t>
-  </si>
-  <si>
-    <t>SECTION A: Medium Level MCQs,MCQ,3,,Fraud detection analytics is commonly used in:,Credit card transactions,Insurance claims,Banking transactions,All of the above,D</t>
-  </si>
-  <si>
-    <t>SECTION A: Medium Level MCQs,MCQ,4,,Supply chain analytics helps businesses:,Increase delivery times,Optimize logistics, reduce costs, and improve efficiency,Hold more inventory,Eliminate suppliers,B</t>
-  </si>
-  <si>
-    <t>SECTION A: Medium Level MCQs,MCQ,5,,HR analytics (People Analytics) is used to:,Randomly hire employees,Improve recruitment, retention, and employee performance,Eliminate performance reviews,Reduce salaries,B</t>
-  </si>
-  <si>
-    <t>SECTION A: Medium Level MCQs,MCQ,6,,Sentiment analysis, which analyzes customer reviews and social media posts, is an application of:,Text analytics and NLP,Financial analytics,Supply chain analytics,HR analytics,A</t>
-  </si>
-  <si>
-    <t>SECTION A: Medium Level MCQs,MCQ,7,,Real-time analytics is used in applications like:,Credit card fraud detection (immediate alert),Monthly sales reports,Annual financial statements,Year-end inventory count,A</t>
-  </si>
-  <si>
-    <t>SECTION B: Scenario-Based Questions,Scenario,8,An online store uses analytics to show ""Customers who bought this also bought..."",This is an application of:,Market basket analysis,Price optimization,Employee scheduling,Financial forecasting,A</t>
-  </si>
-  <si>
-    <t>SECTION B: Scenario-Based Questions,Scenario,9,A supermarket uses loyalty card data to send personalized coupons.,This application is called:,Random marketing,Targeted marketing based on customer behavior,Mass advertising,Social media marketing,B</t>
-  </si>
-  <si>
-    <t>SECTION B: Scenario-Based Questions,Scenario,10,A streaming service uses viewing history to recommend shows.,This application of analytics:,Increases customer engagement and retention,Decreases user satisfaction,Has no impact,Only works for movies,A</t>
-  </si>
-  <si>
-    <t>SECTION B: Scenario-Based Questions,Scenario,11,A hotel uses demand forecasting to adjust room prices.,This application is called:,Dynamic pricing,Fixed pricing,Cost-based pricing,Random pricing,A</t>
-  </si>
-  <si>
-    <t>SECTION B: Scenario-Based Questions,Scenario,12,A manufacturing company uses analytics to predict when machines need maintenance.,This application is called:,Reactive maintenance,Predictive maintenance,Breakdown maintenance,Random maintenance,B</t>
-  </si>
-  <si>
-    <t>SECTION C: Dataset,Dataset,Source,,Spend ($),Impressions,Clicks,Conversions,Revenue ($)</t>
-  </si>
-  <si>
-    <t>SECTION C: Dataset,Dataset,Email,,2000,50000,2500,125,12500</t>
-  </si>
-  <si>
-    <t>SECTION C: Dataset,Dataset,Social Media,,5000,120000,4800,240,24000</t>
-  </si>
-  <si>
-    <t>SECTION C: Dataset,Dataset,Search Ads,,8000,80000,6400,320,32000</t>
-  </si>
-  <si>
-    <t>SECTION C: Dataset,Dataset,Display Ads,,3000,200000,2000,80,8000</t>
-  </si>
-  <si>
-    <t>SECTION C: Dataset,Dataset,TV,,15000,500000,3000,150,15000</t>
-  </si>
-  <si>
-    <t>SECTION C: Practical Questions,Practical,13,,Calculate the Click-Through Rate (CTR) = (Clicks ÷ Impressions) × 100 for each channel. Which channel has the highest CTR?,,,,,</t>
-  </si>
-  <si>
-    <t>SECTION C: Practical Questions,Practical,14,,Calculate the Conversion Rate = (Conversions ÷ Clicks) × 100 for each channel. Which channel has the highest conversion rate?,,,,,</t>
-  </si>
-  <si>
-    <t>SECTION C: Practical Questions,Practical,15,,Calculate the ROI = (Revenue - Spend) ÷ Spend × 100 for each channel. Which channel has the highest ROI?,,,,,</t>
-  </si>
-  <si>
-    <t>SECTION C: Practical Questions,Practical,16,,Calculate the Cost per Conversion = Spend ÷ Conversions for each channel. Which channel has the lowest cost per conversion?,,,,,</t>
-  </si>
-  <si>
-    <t>SECTION C: Practical Questions,Practical,17,,If you had an additional $5,000 to spend, which channel would you invest in based on ROI? Why?,,,,,</t>
-  </si>
-  <si>
-    <t>SECTION C: Practical Questions,Practical,18,,Which channel is most efficient at generating impressions per dollar spent? Show your calculation.,,,,,</t>
-  </si>
-  <si>
-    <t>SECTION C: Practical Questions,Practical,19,,Create a simple ranking of channels from best to worst based on ROI. Show the ranking order.,,,,,</t>
-  </si>
-  <si>
-    <t>SECTION C: Practical Questions,Practical,20,,Write a brief recommendation to the marketing manager about which channels to increase budget and which to decrease.,,,,,</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -151,21 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -465,144 +419,1045 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{917721BB-E4CE-4A68-9FD5-13556550FBE3}">
-  <dimension ref="A1:A30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>. Application of Business Analytics</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Customer churn analysis is an application of business analytics used to:</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SECTION A: Medium Level MCQs</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Predict which customers are likely to stop doing business</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Calculate employee salaries</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Design new products</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Schedule maintenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>. Application of Business Analytics</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Price optimization using analytics helps businesses:</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SECTION A: Medium Level MCQs</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Set random prices</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Find the optimal price to maximize profit or revenue</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Always set the lowest price</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Ignore competitor pricing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>. Application of Business Analytics</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Fraud detection analytics is commonly used in:</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SECTION A: Medium Level MCQs</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Credit card transactions</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Insurance claims</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Banking transactions</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>All of the above</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>. Application of Business Analytics</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Supply chain analytics helps businesses:</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SECTION A: Medium Level MCQs</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Increase delivery times</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Optimize logistics, reduce costs, and improve efficiency</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Hold more inventory</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Eliminate suppliers</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>. Application of Business Analytics</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>HR analytics (People Analytics) is used to:</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SECTION A: Medium Level MCQs</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Randomly hire employees</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Improve recruitment, retention, and employee performance</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Eliminate performance reviews</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Reduce salaries</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>. Application of Business Analytics</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Sentiment analysis, which analyzes customer reviews and social media posts, is an application of:</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SECTION A: Medium Level MCQs</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Text analytics and NLP</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Financial analytics</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Supply chain analytics</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>HR analytics</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>. Application of Business Analytics</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Real-time analytics is used in applications like:</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SECTION A: Medium Level MCQs</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Credit card fraud detection (immediate alert)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Monthly sales reports</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Annual financial statements</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Year-end inventory count</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>. Application of Business Analytics</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>This is an application of:</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SECTION B: Scenario-Based Questions | An online store uses analytics to show ""Customers who bought this also bought...""</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Market basket analysis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Price optimization</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Employee scheduling</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Financial forecasting</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>. Application of Business Analytics</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>This application is called:</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SECTION B: Scenario-Based Questions | A supermarket uses loyalty card data to send personalized coupons.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Random marketing</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Targeted marketing based on customer behavior</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Mass advertising</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Social media marketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>. Application of Business Analytics</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>This application of analytics:</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SECTION B: Scenario-Based Questions | A streaming service uses viewing history to recommend shows.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Increases customer engagement and retention</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Decreases user satisfaction</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Has no impact</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Only works for movies</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>. Application of Business Analytics</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>This application is called:</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SECTION B: Scenario-Based Questions | A hotel uses demand forecasting to adjust room prices.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dynamic pricing</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Fixed pricing</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Cost-based pricing</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Random pricing</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>. Application of Business Analytics</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>This application is called:</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SECTION B: Scenario-Based Questions | A manufacturing company uses analytics to predict when machines need maintenance.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Reactive maintenance</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Predictive maintenance</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Breakdown maintenance</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Random maintenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>. Application of Business Analytics</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Dataset columns: Source, Spend ($), Impressions, Clicks, Conversions, Revenue ($)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SECTION C: Dataset</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
         <v>14</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>. Application of Business Analytics</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Dataset row - Source: Email | Spend ($): 2000 | Impressions: 50000 | Clicks: 2500 | Conversions: 125 | Revenue ($): 12500</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SECTION C: Dataset</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
         <v>15</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>. Application of Business Analytics</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Dataset row - Source: Social Media | Spend ($): 5000 | Impressions: 120000 | Clicks: 4800 | Conversions: 240 | Revenue ($): 24000</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>SECTION C: Dataset</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
         <v>16</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>. Application of Business Analytics</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Dataset row - Source: Search Ads | Spend ($): 8000 | Impressions: 80000 | Clicks: 6400 | Conversions: 320 | Revenue ($): 32000</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>SECTION C: Dataset</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
         <v>17</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>. Application of Business Analytics</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Dataset row - Source: Display Ads | Spend ($): 3000 | Impressions: 200000 | Clicks: 2000 | Conversions: 80 | Revenue ($): 8000</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SECTION C: Dataset</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
         <v>18</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>. Application of Business Analytics</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Dataset row - Source: TV | Spend ($): 15000 | Impressions: 500000 | Clicks: 3000 | Conversions: 150 | Revenue ($): 15000</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SECTION C: Dataset</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
         <v>19</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>. Application of Business Analytics</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Calculate the Click-Through Rate (CTR) = (Clicks ÷ Impressions) × 100 for each channel. Which channel has the highest CTR?</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SECTION C: Practical Questions</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
         <v>20</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>. Application of Business Analytics</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Calculate the Conversion Rate = (Conversions ÷ Clicks) × 100 for each channel. Which channel has the highest conversion rate?</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SECTION C: Practical Questions</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
         <v>21</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>. Application of Business Analytics</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Calculate the ROI = (Revenue - Spend) ÷ Spend × 100 for each channel. Which channel has the highest ROI?</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SECTION C: Practical Questions</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
         <v>22</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>. Application of Business Analytics</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Calculate the Cost per Conversion = Spend ÷ Conversions for each channel. Which channel has the lowest cost per conversion?</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>SECTION C: Practical Questions</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
         <v>23</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>. Application of Business Analytics</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>If you had an additional $5</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>SECTION C: Practical Questions</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>000 to spend</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>which channel would you invest in based on ROI? Why?</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
         <v>24</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>. Application of Business Analytics</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Which channel is most efficient at generating impressions per dollar spent? Show your calculation.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>SECTION C: Practical Questions</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
         <v>25</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>. Application of Business Analytics</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Create a simple ranking of channels from best to worst based on ROI. Show the ranking order.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>SECTION C: Practical Questions</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
         <v>26</v>
       </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>. Application of Business Analytics</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Write a brief recommendation to the marketing manager about which channels to increase budget and which to decrease.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>SECTION C: Practical Questions</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
